--- a/config/data/StateSlotReset.xlsx
+++ b/config/data/StateSlotReset.xlsx
@@ -1,103 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="StateSlotReset" sheetId="1" r:id="rId1"/>
+    <sheet name="StateSlotReset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>StateSlotReset</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>list</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>98bb268a27cc0f00</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>state_slot_id</t>
-  </si>
-  <si>
-    <t>sequence</t>
-  </si>
-  <si>
-    <t>reset_point</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>ref&lt;StateSlot.id&gt;</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>enum&lt;SlotResetPoint&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>range=1..100</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -410,106 +407,181 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>StateSlotReset</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>98bb268a27cc0f00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>state_slot_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>reset_point</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>state_slot_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sequence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>reset_point</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ref&lt;StateSlot.id&gt;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enum&lt;SlotResetPoint&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>range=1..100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>24109</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TurnStart</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/StateSlotReset.xlsx
+++ b/config/data/StateSlotReset.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,19 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>24003</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BattleStart</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/StateSlotReset.xlsx
+++ b/config/data/StateSlotReset.xlsx
@@ -1,39 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="StateSlotReset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="StateSlotReset" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+  <si>
+    <t>@table</t>
+  </si>
+  <si>
+    <t>StateSlotReset</t>
+  </si>
+  <si>
+    <t>@mode</t>
+  </si>
+  <si>
+    <t>list</t>
+  </si>
+  <si>
+    <t>@key</t>
+  </si>
+  <si>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
+  </si>
+  <si>
+    <t>@schema</t>
+  </si>
+  <si>
+    <t>ffa9061a4f22b40a</t>
+  </si>
+  <si>
+    <t>#name</t>
+  </si>
+  <si>
+    <t>state_slot_id</t>
+  </si>
+  <si>
+    <t>sequence</t>
+  </si>
+  <si>
+    <t>reset_point</t>
+  </si>
+  <si>
+    <t>#field</t>
+  </si>
+  <si>
+    <t>#type</t>
+  </si>
+  <si>
+    <t>ref&lt;StateSlot.id&gt;</t>
+  </si>
+  <si>
+    <t>i32</t>
+  </si>
+  <si>
+    <t>enum&lt;SlotResetPoint&gt;</t>
+  </si>
+  <si>
+    <t>#groups</t>
+  </si>
+  <si>
+    <t>#input</t>
+  </si>
+  <si>
+    <t>range=1..100</t>
+  </si>
+  <si>
+    <t>#desc</t>
+  </si>
+  <si>
+    <t>24109</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>TurnStart</t>
+  </si>
+  <si>
+    <t>24003</t>
+  </si>
+  <si>
+    <t>BattleStart</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="8">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,85 +178,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -407,197 +510,152 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="5" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>@table</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>StateSlotReset</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>@mode</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>@key</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>@schema</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>98bb268a27cc0f00</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>#name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>state_slot_id</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>sequence</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>reset_point</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>#field</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>state_slot_id</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sequence</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>reset_point</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>#type</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ref&lt;StateSlot.id&gt;</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>i32</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>enum&lt;SlotResetPoint&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>#input</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>range=1..100</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>#desc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="n">
-        <v>24109</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TurnStart</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="n">
-        <v>24003</v>
-      </c>
-      <c r="C9" t="n">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>BattleStart</t>
-        </is>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="42" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 100." promptTitle="Integer range" prompt="Enter an integer from 1 to 100." sqref="C8:C1007">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: ActivityStart, SectionStart, NodeStart, AttemptStart, BattleStart, WaveStart, TurnStart, ActionStart, HitStart, TurnEnd, ActionEnd, WaveEnd, BattleEnd" promptTitle="SlotResetPoint enum" prompt="Select a value from the dropdown." sqref="D8:D1007">
+      <formula1>"ActivityStart,SectionStart,NodeStart,AttemptStart,BattleStart,WaveStart,TurnStart,ActionStart,HitStart,TurnEnd,ActionEnd,WaveEnd,BattleEnd"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>